--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/sourcing_pipeline.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/sourcing_pipeline.xlsx
@@ -479,16 +479,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="4">
@@ -499,16 +499,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kyriba SI</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Intake</t>
+          <t>RFP</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Reporting tool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RFP</t>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.8</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -559,16 +559,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RFP</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.7</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Kyriba SI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23.8</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="9">
@@ -599,16 +599,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Reporting tool</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RFP</t>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -619,16 +619,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Kyriba SI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BAFO</t>
+          <t>RFI</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -639,16 +639,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>RFP</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12">
@@ -659,16 +659,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Award</t>
+          <t>BAFO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>37.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="13">
@@ -679,7 +679,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kyriba SI</t>
+          <t>Cyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="14">
@@ -699,16 +699,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>34.9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="15">
@@ -719,16 +719,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Reporting tool</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.4</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -744,11 +744,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Intake</t>
+          <t>Award</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.199999999999999</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="17">
@@ -759,16 +759,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMS RFP</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>RFP</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.5</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="18">
@@ -779,16 +779,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cyber</t>
+          <t>Reporting tool</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Intake</t>
+          <t>RFP</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="19">
@@ -799,16 +799,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reporting tool</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RFI</t>
+          <t>Intake</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5.7</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="20">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.2</v>
+        <v>27.9</v>
       </c>
     </row>
   </sheetData>
